--- a/Internship_artifacts/Defect_Tracker Template_v0.1.xlsx
+++ b/Internship_artifacts/Defect_Tracker Template_v0.1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manma\Desktop\final year project files all\Internship_artifacts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manma\Desktop\Langchain_project\Internship_artifacts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EE45EA9-0FB3-48BD-81EF-BCD6F5F1210C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72C75700-D54E-45DF-B732-EEEB707AA0B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -92,9 +92,6 @@
     <t>Context working</t>
   </si>
   <si>
-    <t>Added final answer enforcement and output handling</t>
-  </si>
-  <si>
     <t>Sprint 4</t>
   </si>
   <si>
@@ -113,15 +110,9 @@
     <t>LangChain environment setup failed due to dependency conflicts</t>
   </si>
   <si>
-    <t>Resolved dependency issues and installed compatible versions</t>
-  </si>
-  <si>
     <t>Tested successfully</t>
   </si>
   <si>
-    <t>LLM connection failed while integrating Groq API</t>
-  </si>
-  <si>
     <t>API</t>
   </si>
   <si>
@@ -146,48 +137,30 @@
     <t>Fixed API request and response parsing logic</t>
   </si>
   <si>
-    <t>Agent fails when chaining multiple tools, incorrect execution flow</t>
-  </si>
-  <si>
     <t>Fixed tool chaining logic in LangChain orchestration</t>
   </si>
   <si>
     <t>Workflow validated</t>
   </si>
   <si>
-    <t>Agent asking user which tool to use instead of auto selection</t>
-  </si>
-  <si>
     <t>Logic</t>
   </si>
   <si>
-    <t>Improved system prompt to enforce tool usage</t>
-  </si>
-  <si>
     <t>Working correctly</t>
   </si>
   <si>
-    <t>Response time too high for multi-agent tasks</t>
-  </si>
-  <si>
     <t>Performance</t>
   </si>
   <si>
     <t>Optimized prompt handling and reduced token usage</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>Open</t>
   </si>
   <si>
     <t>Needs further tuning</t>
   </si>
   <si>
-    <t>Memory not storing previous conversation context</t>
-  </si>
-  <si>
     <t>Fixed shared memory configuration and update logic</t>
   </si>
   <si>
@@ -200,9 +173,6 @@
     <t>Accuracy improved</t>
   </si>
   <si>
-    <t>Agent stops at Thought or Action without final answer</t>
-  </si>
-  <si>
     <t>Issue resolved</t>
   </si>
   <si>
@@ -212,15 +182,9 @@
     <t>Backend</t>
   </si>
   <si>
-    <t>Fixed API route and response formatting</t>
-  </si>
-  <si>
     <t>API verified</t>
   </si>
   <si>
-    <t>UI not showing agent output correctly</t>
-  </si>
-  <si>
     <t>UI</t>
   </si>
   <si>
@@ -245,9 +209,6 @@
     <t>Feature</t>
   </si>
   <si>
-    <t>Handled null pages and limited extraction size</t>
-  </si>
-  <si>
     <t>Feature working</t>
   </si>
   <si>
@@ -264,13 +225,52 @@
   </si>
   <si>
     <t>Needs optimization</t>
+  </si>
+  <si>
+    <t>Resolved dependency conflicts and installed compatible versions</t>
+  </si>
+  <si>
+    <t>LLM connection failed during Groq API integration</t>
+  </si>
+  <si>
+    <t>Agent fails when chaining multiple tools due to incorrect execution flow</t>
+  </si>
+  <si>
+    <t>Agent asking user to choose tool instead of automatic selection</t>
+  </si>
+  <si>
+    <t>Improved system prompt to enforce automatic tool usage</t>
+  </si>
+  <si>
+    <t>High response time observed in multi-agent execution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- </t>
+  </si>
+  <si>
+    <t>Memory not storing previous conversation context correctly</t>
+  </si>
+  <si>
+    <t>Agent stops at Thought or Action stage without final output</t>
+  </si>
+  <si>
+    <t>Implemented final answer enforcement and output handling</t>
+  </si>
+  <si>
+    <t>Fixed API routes and response formatting</t>
+  </si>
+  <si>
+    <t>UI not displaying agent output correctly</t>
+  </si>
+  <si>
+    <t>Handled null pages and optimized extraction logic</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -298,12 +298,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -347,7 +341,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -355,8 +349,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="15" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="15" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -668,7 +661,7 @@
     <col min="2" max="2" width="15" style="3" customWidth="1"/>
     <col min="3" max="3" width="21.88671875" style="3" customWidth="1"/>
     <col min="4" max="4" width="69.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16" style="3" customWidth="1"/>
     <col min="6" max="6" width="18.5546875" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.21875" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="66.109375" style="3" bestFit="1" customWidth="1"/>
@@ -678,7 +671,7 @@
     <col min="12" max="16384" width="17.5546875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" s="4" customFormat="1" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -713,603 +706,564 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A2" s="5">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="5">
+        <v>46073</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="6">
-        <v>46073</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="I2" s="5">
+        <v>46074</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="5" t="s">
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="5">
+        <v>46074</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" s="5">
+        <v>46074</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="I2" s="6">
-        <v>46074</v>
-      </c>
-      <c r="J2" s="5" t="s">
+      <c r="C4" s="5">
+        <v>46076</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" s="5">
+        <v>46077</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A3" s="5">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="6">
-        <v>46074</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" s="5" t="s">
+      <c r="K4" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="5">
+        <v>46082</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" s="5">
+        <v>46083</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="5">
+        <v>46084</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I7" s="5">
+        <v>46085</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="5">
+        <v>46087</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="I8" s="5">
+        <v>46088</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="5">
+        <v>46090</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="5">
+        <v>46095</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I11" s="5">
+        <v>46096</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="5">
+        <v>46097</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I12" s="5">
+        <v>46098</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="5">
+        <v>46099</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="I13" s="5">
+        <v>46100</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <v>11</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="5">
+        <v>46106</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="I15" s="5">
+        <v>46107</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <v>12</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="5">
+        <v>46109</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="I16" s="5">
+        <v>46110</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <v>13</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="5">
+        <v>46113</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="I17" s="5">
+        <v>46114</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <v>14</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="5">
+        <v>46115</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I18" s="5">
+        <v>46116</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="3">
+        <v>15</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="5">
+        <v>46116</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="I19" s="5">
+        <v>46117</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
         <v>16</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="B20" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I3" s="6">
-        <v>46074</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A4" s="5">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="6">
-        <v>46076</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4" s="6">
-        <v>46077</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-    </row>
-    <row r="6" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A6" s="5">
-        <v>4</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="6">
-        <v>46082</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="I6" s="6">
-        <v>46083</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A7" s="5">
-        <v>5</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="6">
-        <v>46084</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="H7" s="5" t="s">
+      <c r="C20" s="5">
+        <v>46117</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="I7" s="6">
-        <v>46085</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A8" s="5">
-        <v>6</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="6">
-        <v>46087</v>
-      </c>
-      <c r="D8" s="5" t="s">
+      <c r="H20" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="I20" s="5">
+        <v>46117</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I8" s="6">
-        <v>46088</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A9" s="5">
-        <v>7</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="6">
-        <v>46090</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="K9" s="5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-    </row>
-    <row r="11" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A11" s="5">
-        <v>8</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="6">
-        <v>46095</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="I11" s="6">
-        <v>46096</v>
-      </c>
-      <c r="J11" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K11" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A12" s="5">
-        <v>9</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="6">
-        <v>46097</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="I12" s="6">
-        <v>46098</v>
-      </c>
-      <c r="J12" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K12" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A13" s="5">
-        <v>10</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="6">
-        <v>46099</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I13" s="6">
-        <v>46100</v>
-      </c>
-      <c r="J13" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K13" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-    </row>
-    <row r="15" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A15" s="5">
-        <v>11</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" s="6">
-        <v>46106</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="I15" s="6">
-        <v>46107</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K15" s="5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A16" s="5">
-        <v>12</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" s="6">
-        <v>46109</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="H16" s="5" t="s">
+      <c r="K20" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="I16" s="6">
-        <v>46110</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K16" s="5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A17" s="5">
-        <v>13</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" s="6">
-        <v>46113</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="I17" s="6">
-        <v>46114</v>
-      </c>
-      <c r="J17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K17" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A18" s="5">
-        <v>14</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C18" s="6">
-        <v>46115</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="I18" s="6">
-        <v>46116</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K18" s="5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A19" s="5">
-        <v>15</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" s="6">
-        <v>46116</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="I19" s="6">
-        <v>46117</v>
-      </c>
-      <c r="J19" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K19" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="A20" s="5">
-        <v>16</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" s="6">
-        <v>46117</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="I20" s="6">
-        <v>46117</v>
-      </c>
-      <c r="J20" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="K20" s="5" t="s">
-        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -1369,12 +1323,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F50FC49184C87E449886FB52439922C9" ma:contentTypeVersion="2" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f85b7e58c3d8889ba0673e7b34a193a6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b67b99c0-208c-4860-83e0-51466af787c4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5d43477c1ade21a66d9a75ba2d5aa042" ns2:_="">
     <xsd:import namespace="b67b99c0-208c-4860-83e0-51466af787c4"/>
@@ -1506,6 +1454,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -1516,15 +1470,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B149665-BEBB-4C97-BAA6-72374EAA67F9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{191CB444-B9BF-4C91-94BD-600524521497}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1542,6 +1487,15 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B149665-BEBB-4C97-BAA6-72374EAA67F9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20D196DE-5AC8-4D3B-8CD7-1A2AE6EEDD72}">
   <ds:schemaRefs>
